--- a/output/pdf_financials_xlsx/ARX.xlsx
+++ b/output/pdf_financials_xlsx/ARX.xlsx
@@ -6811,43 +6811,43 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0001133</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-5.04e-05</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.5e-05</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1e-05</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>1.3e-05</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-3.629999999999999e-05</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0001167</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0601</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0021</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-6.400000000000001e-06</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.18e-05</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-3.12e-05</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-5.36e-05</v>
       </c>
     </row>
     <row r="119">
@@ -23011,7 +23011,11 @@
           <t>Exploration and evaluation asset expenditures (Note 8)</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -25326,7 +25330,11 @@
           <t>Exploration and evaluation asset expenditures (Note 7)</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -28937,7 +28945,11 @@
           <t>Exploration and evaluation asset expenditures (Note 10)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -29289,7 +29301,11 @@
           <t>Exploration and evaluation expenses (Note 10)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -31886,7 +31902,11 @@
           <t>Exploration and evaluation expenses (Note 9, 11)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -32515,7 +32535,11 @@
           <t>Exploration and evaluation asset expenditures (Note 9)</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -34924,7 +34948,11 @@
           <t>Intangible exploration and evaluation asset expenditures (Note 9)</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -37349,7 +37377,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ARX.xlsx
+++ b/output/pdf_financials_xlsx/ARX.xlsx
@@ -902,28 +902,28 @@
         <v>0.0017869</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.0006951</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.0009727000000000001</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1.1774</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>1.1797</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.004682100000000001</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.0039645</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.0039369</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.0044732</v>
       </c>
     </row>
     <row r="11">
@@ -954,10 +954,10 @@
         <v>-0.0006965</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.0009745</v>
+        <v>0.0002794</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.0011229</v>
+        <v>0.0001502</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.005099</v>
+        <v>0.0011621</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.0060757</v>
+        <v>0.0016025</v>
       </c>
     </row>
     <row r="12">
@@ -1017,13 +1017,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>6.2e-06</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1881,13 +1881,13 @@
         <v>0.0002427</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.0005248</v>
+        <v>0.0005185999999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.3218</v>
+        <v>0.3133</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.1285</v>
+        <v>-0.1333</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>0.0029782</v>
@@ -1985,13 +1985,13 @@
         <v>0.0002427</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.0005248</v>
+        <v>0.0005185999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.3218</v>
+        <v>0.3133</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.1285</v>
+        <v>-0.1333</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>0.0029782</v>
@@ -2041,7 +2041,7 @@
         <v>24.90507952796306</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>46.73612966426217</v>
+        <v>46.18398788850297</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -43420,7 +43420,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -44320,7 +44320,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
